--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1707-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1707-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97A2BC42-0AF5-419B-93C8-95DECA10C678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8F6CD06-A5FD-4553-8D1C-6892F43BAF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{34E7DEA1-2248-4730-80AA-DFF70432A378}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{38F2BD7A-AB07-493B-94C9-8AB7BB85CD41}"/>
   </bookViews>
   <sheets>
     <sheet name="1707-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1492,23 +1492,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B196A92E-CD33-4456-8EB8-C11E8596F3F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42AB0ADF-A363-4854-974C-E98444478546}">
   <dimension ref="A1:R49"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1536,7 +1535,7 @@
       <c r="Q1" s="33"/>
       <c r="R1" s="25"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1566,7 +1565,7 @@
       <c r="Q2" s="35"/>
       <c r="R2" s="36"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1612,7 +1611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1662,7 +1661,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="40">
         <v>2026</v>
       </c>
@@ -1716,7 +1715,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="42"/>
       <c r="B6" s="43"/>
       <c r="C6" s="45"/>
@@ -1742,7 +1741,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1798,7 +1797,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="50">
         <v>2025</v>
       </c>
@@ -1852,7 +1851,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1908,7 +1907,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -1964,7 +1963,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="52">
         <v>2024</v>
       </c>
@@ -2018,7 +2017,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="50">
         <v>2023</v>
       </c>
@@ -2072,7 +2071,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="52">
         <v>2022</v>
       </c>
@@ -2126,7 +2125,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="50">
         <v>2021</v>
       </c>
@@ -2180,7 +2179,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="52">
         <v>2020</v>
       </c>
@@ -2234,7 +2233,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="50">
         <v>2019</v>
       </c>
@@ -2288,7 +2287,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="52">
         <v>2018</v>
       </c>
@@ -2342,7 +2341,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="50">
         <v>2017</v>
       </c>
@@ -2396,7 +2395,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="52">
         <v>2016</v>
       </c>
@@ -2450,7 +2449,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="50">
         <v>2015</v>
       </c>
@@ -2504,7 +2503,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="52">
         <v>2014</v>
       </c>
@@ -2558,7 +2557,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="50">
         <v>2013</v>
       </c>
@@ -2612,7 +2611,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="52">
         <v>2012</v>
       </c>
@@ -2666,7 +2665,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="50">
         <v>2011</v>
       </c>
@@ -2720,7 +2719,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="52">
         <v>2010</v>
       </c>
@@ -2774,7 +2773,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="50">
         <v>2009</v>
       </c>
@@ -2828,7 +2827,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="52">
         <v>2008</v>
       </c>
@@ -2882,7 +2881,7 @@
         <v>6.19</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="50">
         <v>2007</v>
       </c>
@@ -2936,7 +2935,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="52">
         <v>2006</v>
       </c>
@@ -2990,7 +2989,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="50">
         <v>2005</v>
       </c>
@@ -3044,7 +3043,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="52">
         <v>2004</v>
       </c>
@@ -3098,7 +3097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="50">
         <v>2003</v>
       </c>
@@ -3152,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="52">
         <v>2002</v>
       </c>
@@ -3206,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="50">
         <v>2001</v>
       </c>
@@ -3260,7 +3259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="52">
         <v>2000</v>
       </c>
@@ -3314,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="50">
         <v>1999</v>
       </c>
@@ -3368,7 +3367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="52">
         <v>1998</v>
       </c>
@@ -3422,7 +3421,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="50">
         <v>1997</v>
       </c>
@@ -3476,7 +3475,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="52">
         <v>1996</v>
       </c>
@@ -3530,7 +3529,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="50">
         <v>1995</v>
       </c>
@@ -3584,7 +3583,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="52">
         <v>1994</v>
       </c>
@@ -3638,7 +3637,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="50">
         <v>1993</v>
       </c>
@@ -3692,7 +3691,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="52">
         <v>1992</v>
       </c>
@@ -3746,7 +3745,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="50">
         <v>1990</v>
       </c>
@@ -3800,7 +3799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="52">
         <v>1989</v>
       </c>
@@ -3854,7 +3853,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="50">
         <v>1988</v>
       </c>
@@ -3908,7 +3907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="52">
         <v>1985</v>
       </c>
@@ -3962,7 +3961,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="50">
         <v>1984</v>
       </c>
@@ -4016,7 +4015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="52" t="s">
         <v>34</v>
       </c>
